--- a/tame_output/ON/bt/strategyON_20240420.xlsx
+++ b/tame_output/ON/bt/strategyON_20240420.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-13.0%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>53.3%</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.4%</t>
+          <t>-79.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>117.7%</t>
+          <t>116.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>138.1%</t>
+          <t>136.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.7%</t>
+          <t>95.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-722.5%</t>
+          <t>-705.9%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-58.0%</t>
+          <t>-57.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.4%</t>
+          <t>-74.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>96.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>781.0%</t>
+          <t>788.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-2.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-567.1%</t>
+          <t>-566.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.8%</t>
+          <t>99.7%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-283.6%</t>
+          <t>-277.0%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-45.4%</t>
+          <t>-44.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-50.6%</t>
+          <t>-41.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-262.8%</t>
+          <t>-262.7%</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-27.2%</t>
+          <t>-26.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-160.2%</t>
+          <t>-161.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.6%</t>
+          <t>-16.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>33.5%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330518</v>
+        <v>3.300815818330519</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.968320582393223</v>
+        <v>-6.802755682476709</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.322941295144096</v>
+        <v>0.389167255110701</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.799118819568881</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.38471245668022</v>
+        <v>-7.219147556763707</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1543785960381743</v>
+        <v>0.2206045560047798</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.799118819568881</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.761389467210065</v>
+        <v>-7.595824567293551</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.0139664824949155</v>
+        <v>0.08019244246152102</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.799118819568881</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.107264289194873</v>
+        <v>-7.94169938927836</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.1282838811533127</v>
+        <v>-0.06205792118670761</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.799118819568881</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.420089088439852</v>
+        <v>-8.254524188523339</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.2550088807963031</v>
+        <v>-0.1887829208296981</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.799118819568881</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.71675043025005</v>
+        <v>-8.551185530333537</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3698944415911742</v>
+        <v>-0.3036684816245692</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.867861955302759</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.150099538360285</v>
+        <v>-8.984534638443773</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.5472603893696717</v>
+        <v>-0.4810344294030666</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.867861955302759</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.533100927102916</v>
+        <v>-9.367536027186404</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.7005630461883081</v>
+        <v>-0.634337086221703</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.867861955302759</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.908086253274194</v>
+        <v>-9.742521353357681</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.8479856606853891</v>
+        <v>-0.781759700718784</v>
       </c>
       <c r="F1873" t="n">
         <v>-2.242847281474037</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.2676165757782</v>
+        <v>-10.10205167586168</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.986447486388939</v>
+        <v>-0.9202215264223339</v>
       </c>
       <c r="F1874" t="n">
         <v>-2.242847281474037</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.59401660444321</v>
+        <v>-10.4284517045267</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.109091477897767</v>
+        <v>-1.042865517931162</v>
       </c>
       <c r="F1875" t="n">
         <v>-2.56924731013905</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.81316557251741</v>
+        <v>-10.64760067260089</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.193709314505677</v>
+        <v>-1.127483354539072</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.788396278213247</v>
@@ -44722,10 +44722,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.80947464756099</v>
+        <v>-10.64390974764448</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.192232944523113</v>
+        <v>-1.126006984556508</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.788396278213247</v>
@@ -44745,10 +44745,10 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-11.01373282289086</v>
+        <v>-10.84816792297435</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.268423017536416</v>
+        <v>-1.202197057569811</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.916035222827236</v>
@@ -44768,10 +44768,10 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.23177059452204</v>
+        <v>-11.06620569460552</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.351155571704451</v>
+        <v>-1.284929611737846</v>
       </c>
       <c r="F1879" t="n">
         <v>-3.090805990923135</v>
@@ -44791,10 +44791,10 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-11.15830076285459</v>
+        <v>-10.99273586293807</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.306395937544051</v>
+        <v>-1.240169977577446</v>
       </c>
       <c r="F1880" t="n">
         <v>-3.017336159255687</v>
@@ -44814,10 +44814,10 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.33342518024113</v>
+        <v>-11.16786028032462</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.361890483751151</v>
+        <v>-1.295664523784546</v>
       </c>
       <c r="F1881" t="n">
         <v>-3.19246057664223</v>
@@ -44837,10 +44837,10 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.56787727425562</v>
+        <v>-11.40231237433911</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.462890486258543</v>
+        <v>-1.396664526291938</v>
       </c>
       <c r="F1882" t="n">
         <v>-3.19246057664223</v>
@@ -44860,10 +44860,10 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.85568111879286</v>
+        <v>-11.69011621887635</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.584684214847414</v>
+        <v>-1.518458254880809</v>
       </c>
       <c r="F1883" t="n">
         <v>-3.480264421179469</v>
@@ -44883,10 +44883,10 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-12.08550556595668</v>
+        <v>-11.91994066604017</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.675498203874388</v>
+        <v>-1.609272243907783</v>
       </c>
       <c r="F1884" t="n">
         <v>-3.642911958249629</v>
@@ -44906,10 +44906,10 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.31753448569295</v>
+        <v>-12.15196958577643</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.765616043139778</v>
+        <v>-1.699390083173173</v>
       </c>
       <c r="F1885" t="n">
         <v>-3.704924655438052</v>
@@ -44929,10 +44929,10 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.26551897172413</v>
+        <v>-12.09995407180762</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.740819501865852</v>
+        <v>-1.674593541899247</v>
       </c>
       <c r="F1886" t="n">
         <v>-3.704924655438052</v>
@@ -44952,10 +44952,10 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.40719081344825</v>
+        <v>-12.24162591353174</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.798963465454242</v>
+        <v>-1.732737505487637</v>
       </c>
       <c r="F1887" t="n">
         <v>-3.704924655438052</v>
@@ -44975,10 +44975,10 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.50609755390753</v>
+        <v>-12.34053265399102</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.82347275147308</v>
+        <v>-1.757246791506474</v>
       </c>
       <c r="F1888" t="n">
         <v>-3.803831395897328</v>
@@ -44998,10 +44998,10 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.30694544667043</v>
+        <v>-12.14138054675392</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.756863042224924</v>
+        <v>-1.690637082258319</v>
       </c>
       <c r="F1889" t="n">
         <v>-3.638508869947514</v>
@@ -45021,10 +45021,10 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-12.08110029395102</v>
+        <v>-11.91553539403451</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.65694590810095</v>
+        <v>-1.590719948134346</v>
       </c>
       <c r="F1890" t="n">
         <v>-3.596582194360351</v>
@@ -45044,10 +45044,10 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.79482548162832</v>
+        <v>-11.62926058171181</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.541296838615813</v>
+        <v>-1.475070878649209</v>
       </c>
       <c r="F1891" t="n">
         <v>-3.596582194360351</v>
@@ -45067,10 +45067,10 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.84772076967261</v>
+        <v>-11.6821558697561</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.559821179671419</v>
+        <v>-1.493595219704815</v>
       </c>
       <c r="F1892" t="n">
         <v>-3.591626848271904</v>
@@ -45090,10 +45090,10 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.56381203874386</v>
+        <v>-11.39824713882735</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.440523983061284</v>
+        <v>-1.37429802309468</v>
       </c>
       <c r="F1893" t="n">
         <v>-3.591626848271904</v>
@@ -45113,10 +45113,10 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.44839111460576</v>
+        <v>-11.28282621468925</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.40409287579991</v>
+        <v>-1.337866915833306</v>
       </c>
       <c r="F1894" t="n">
         <v>-3.476205924133809</v>
@@ -45136,10 +45136,10 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.18455424740169</v>
+        <v>-11.01898934748518</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.30844161023119</v>
+        <v>-1.242215650264586</v>
       </c>
       <c r="F1895" t="n">
         <v>-3.476205924133809</v>
@@ -45159,10 +45159,10 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.9173124465333</v>
+        <v>-10.75174754661679</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.203379450383205</v>
+        <v>-1.137153490416601</v>
       </c>
       <c r="F1896" t="n">
         <v>-3.476205924133809</v>
@@ -45182,10 +45182,10 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.79400651805508</v>
+        <v>-10.62844161813857</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.154357393965378</v>
+        <v>-1.088131433998774</v>
       </c>
       <c r="F1897" t="n">
         <v>-3.386788253006246</v>
@@ -45205,10 +45205,10 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.77005297707912</v>
+        <v>-10.60448807716261</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.144107471429501</v>
+        <v>-1.077881511462897</v>
       </c>
       <c r="F1898" t="n">
         <v>-3.362834712030288</v>
@@ -45228,10 +45228,10 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.50599303875632</v>
+        <v>-10.34042813883981</v>
       </c>
       <c r="E1899" t="n">
-        <v>-1.051743812262135</v>
+        <v>-0.9855178522955299</v>
       </c>
       <c r="F1899" t="n">
         <v>-3.098774773707492</v>
@@ -45251,10 +45251,10 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.798913415251485</v>
+        <v>-9.633348515334974</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.7716989965205006</v>
+        <v>-0.7054730365538964</v>
       </c>
       <c r="F1900" t="n">
         <v>-3.098774773707492</v>
@@ -45274,10 +45274,10 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.758729116885295</v>
+        <v>-9.593164216968784</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.755281653286183</v>
+        <v>-0.6890556933195788</v>
       </c>
       <c r="F1901" t="n">
         <v>-3.058590475341301</v>
@@ -45297,10 +45297,10 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.678659321347491</v>
+        <v>-9.51309442143098</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.7238869138503041</v>
+        <v>-0.6576609538836999</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.978520679803497</v>
@@ -45320,10 +45320,10 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.445178099117893</v>
+        <v>-9.279613199201382</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.622569996120613</v>
+        <v>-0.5563440361540084</v>
       </c>
       <c r="F1903" t="n">
         <v>-2.745039457573899</v>
@@ -45343,10 +45343,10 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.265469568974019</v>
+        <v>-9.099904669057508</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.5535787943760226</v>
+        <v>-0.4873528344094185</v>
       </c>
       <c r="F1904" t="n">
         <v>-2.687867953411203</v>
@@ -45366,10 +45366,10 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-9.133194095343132</v>
+        <v>-8.967629195426621</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.5053011181766407</v>
+        <v>-0.4390751582100365</v>
       </c>
       <c r="F1905" t="n">
         <v>-2.555592479780316</v>
@@ -45389,10 +45389,10 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.942594420669979</v>
+        <v>-8.777029520753468</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.4262461876197428</v>
+        <v>-0.3600202276531381</v>
       </c>
       <c r="F1906" t="n">
         <v>-2.364992805107164</v>
@@ -45412,10 +45412,10 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.693594621986398</v>
+        <v>-8.528029722069887</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.3137399269226515</v>
+        <v>-0.2475139669560469</v>
       </c>
       <c r="F1907" t="n">
         <v>-2.364992805107164</v>
@@ -45435,10 +45435,10 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.799184611759502</v>
+        <v>-8.633619711842991</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4839518524311117</v>
+        <v>-0.4177258924645075</v>
       </c>
       <c r="F1908" t="n">
         <v>-2.470582794880268</v>
@@ -45458,10 +45458,10 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.817919513878099</v>
+        <v>-8.652354613961588</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.4429014714014645</v>
+        <v>-0.3766755114348599</v>
       </c>
       <c r="F1909" t="n">
         <v>-2.470582794880268</v>
@@ -45481,10 +45481,10 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.6699794724705</v>
+        <v>-8.504414572553989</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.5036043775265924</v>
+        <v>-0.4373784175599877</v>
       </c>
       <c r="F1910" t="n">
         <v>-2.45026187897171</v>
@@ -45504,10 +45504,10 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.543087066035429</v>
+        <v>-8.377522166118919</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.4615614012060423</v>
+        <v>-0.3953354412394381</v>
       </c>
       <c r="F1911" t="n">
         <v>-2.323369472536641</v>
@@ -45527,10 +45527,10 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.499538659264738</v>
+        <v>-8.333973759348227</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.4511026505928588</v>
+        <v>-0.3848766906262546</v>
       </c>
       <c r="F1912" t="n">
         <v>-2.323369472536641</v>
@@ -45550,10 +45550,10 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.25739026581088</v>
+        <v>-8.091825365894369</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.3397809388301725</v>
+        <v>-0.2735549788635683</v>
       </c>
       <c r="F1913" t="n">
         <v>-2.323369472536641</v>
@@ -45573,10 +45573,10 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.194160894042533</v>
+        <v>-8.028595994126022</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.3199570696636385</v>
+        <v>-0.2537311096970343</v>
       </c>
       <c r="F1914" t="n">
         <v>-2.323369472536641</v>
@@ -45596,10 +45596,10 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-8.007673201665526</v>
+        <v>-7.842108301749016</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.2478638987022594</v>
+        <v>-0.1816379387356548</v>
       </c>
       <c r="F1915" t="n">
         <v>-2.136881780159634</v>
@@ -45619,10 +45619,10 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.986524002762082</v>
+        <v>-7.820959102845572</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.2317032409035567</v>
+        <v>-0.1654772809369525</v>
       </c>
       <c r="F1916" t="n">
         <v>-2.115732581256191</v>
@@ -45642,10 +45642,10 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.742758560778638</v>
+        <v>-7.577193660862128</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.1384163557631282</v>
+        <v>-0.07219039579652398</v>
       </c>
       <c r="F1917" t="n">
         <v>-2.115732581256191</v>
@@ -45665,10 +45665,10 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.478730493585378</v>
+        <v>-7.313165593668868</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.03068081496580843</v>
+        <v>0.03554514500079575</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.913867182440237</v>
@@ -45688,10 +45688,10 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.228880099636304</v>
+        <v>-7.063315199719794</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.06200141759752364</v>
+        <v>0.1282273775641278</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.913867182440237</v>
@@ -45711,10 +45711,10 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.925312610632325</v>
+        <v>-6.759747710715815</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.1870275367197638</v>
+        <v>0.253253496686368</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.913867182440237</v>
@@ -45734,10 +45734,10 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.851832701780311</v>
+        <v>-6.686267801863801</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.2297470063151228</v>
+        <v>0.2959729662817274</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.840387273588223</v>
@@ -45757,10 +45757,10 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.626799702111488</v>
+        <v>-6.461234802194978</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.3187806837989493</v>
+        <v>0.3850066437655535</v>
       </c>
       <c r="F1922" t="n">
         <v>-1.6153542739194</v>
@@ -45780,10 +45780,10 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.412165324475081</v>
+        <v>-6.246600424558571</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.4093292359078293</v>
+        <v>0.4755551958744335</v>
       </c>
       <c r="F1923" t="n">
         <v>-1.400719896282993</v>
@@ -45803,10 +45803,10 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.14556496750073</v>
+        <v>-5.98000006758422</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4971636374813655</v>
+        <v>0.5633895974479701</v>
       </c>
       <c r="F1924" t="n">
         <v>-1.400719896282993</v>
@@ -45826,10 +45826,10 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.905134470695869</v>
+        <v>-5.739569570779359</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5950789128281873</v>
+        <v>0.6613048727947914</v>
       </c>
       <c r="F1925" t="n">
         <v>-1.160289399478133</v>
@@ -45849,10 +45849,10 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.662343663046424</v>
+        <v>-5.496778763129914</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6961245497227853</v>
+        <v>0.7623505096893899</v>
       </c>
       <c r="F1926" t="n">
         <v>-1.160289399478133</v>
@@ -45872,10 +45872,10 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.422738571439335</v>
+        <v>-5.257173671522825</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7926451702829609</v>
+        <v>0.8588711302495655</v>
       </c>
       <c r="F1927" t="n">
         <v>-1.093241451809638</v>
@@ -45895,10 +45895,10 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.180082983016171</v>
+        <v>-5.014518083099661</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.88670547687222</v>
+        <v>0.9529314368388242</v>
       </c>
       <c r="F1928" t="n">
         <v>-1.093241451809638</v>
@@ -45918,10 +45918,10 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.960062184979161</v>
+        <v>-4.794497285062651</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9762928330976384</v>
+        <v>1.042518793064243</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.9520216067416583</v>
@@ -45941,10 +45941,10 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.760813555074352</v>
+        <v>-4.595248655157842</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.071886467861385</v>
+        <v>1.13811242782799</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.9520216067416583</v>
@@ -45964,10 +45964,10 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.601298451554982</v>
+        <v>-4.435733551638472</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.136838353709435</v>
+        <v>1.203064313676039</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.7925065032222883</v>
@@ -45987,10 +45987,10 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.456626306455244</v>
+        <v>-4.291061406538734</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.20479531431077</v>
+        <v>1.271021274277374</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.647834358122551</v>
@@ -46010,10 +46010,10 @@
         <v>2.903141953293337</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.438856847524288</v>
+        <v>-4.273291947607778</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.127242789969874</v>
+        <v>1.193468749936478</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.6300648991915954</v>
@@ -46033,10 +46033,10 @@
         <v>2.925542446615903</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.352057349745279</v>
+        <v>-4.186492449828769</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.184363082404044</v>
+        <v>1.250589042370648</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.6300648991915954</v>
@@ -46056,10 +46056,10 @@
         <v>2.925614847989315</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.252364735016267</v>
+        <v>-4.086799835099757</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.22431252966906</v>
+        <v>1.290538489635665</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.5303722844625836</v>
@@ -46079,10 +46079,10 @@
         <v>2.936621770464017</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.320734921340278</v>
+        <v>-4.155170021423768</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.207971377614159</v>
+        <v>1.274197337580763</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.5210965854263686</v>
@@ -46102,10 +46102,10 @@
         <v>2.927058479095908</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.199318491713801</v>
+        <v>-4.033753591797291</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.24697465809664</v>
+        <v>1.313200618063245</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.5210965854263686</v>
@@ -46125,10 +46125,10 @@
         <v>2.751768044136295</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.230311651042507</v>
+        <v>-4.064746751125996</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.059286959405545</v>
+        <v>1.125512919372149</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.5210965854263686</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.400112244027663</v>
+        <v>3.81350161240977</v>
       </c>
       <c r="C1939" t="n">
         <v>2.756335276128083</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.054928204634191</v>
+        <v>-4.050858601816048</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.134007569960659</v>
+        <v>1.135635411087917</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.5210965854263686</v>

--- a/tame_output/ON/bt/strategyON_20240420.xlsx
+++ b/tame_output/ON/bt/strategyON_20240420.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.0%</t>
+          <t>-78.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>116.6%</t>
+          <t>116.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.1%</t>
+          <t>95.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.8%</t>
+          <t>-74.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>96.7%</t>
+          <t>97.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-2.1%</t>
+          <t>-2.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-566.7%</t>
+          <t>-550.5%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-262.7%</t>
+          <t>-256.2%</t>
         </is>
       </c>
     </row>
@@ -46148,10 +46148,10 @@
         <v>2.756335276128083</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.050858601816048</v>
+        <v>-3.889272491333527</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.135635411087917</v>
+        <v>1.200269855280925</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.5210965854263686</v>

--- a/tame_output/ON/bt/strategyON_20240420.xlsx
+++ b/tame_output/ON/bt/strategyON_20240420.xlsx
@@ -605,7 +605,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1936</v>
+        <v>1937</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.0%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>60.3%</t>
+          <t>64.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1936</v>
+        <v>1937</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-4.6%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-4.5%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>24.9%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-36.0%</t>
+          <t>-20.7%</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1936</v>
+        <v>1937</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>136.6%</t>
+          <t>136.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.2%</t>
+          <t>-74.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>97.0%</t>
+          <t>96.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1936</v>
+        <v>1937</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.9%</t>
+          <t>70.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1936</v>
+        <v>1937</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1936</v>
+        <v>1937</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>40.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-201.7%</t>
+          <t>-155.8%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1939"/>
+  <dimension ref="A1:G1940"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191734</v>
+        <v>3.302618194191735</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108636</v>
+        <v>3.305023265108637</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097817</v>
+        <v>3.341378723097818</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094114</v>
+        <v>3.374439043094115</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199283</v>
+        <v>3.405960511199284</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923085</v>
+        <v>3.419979433923086</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297748</v>
+        <v>3.458100091297749</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317615</v>
+        <v>3.447750501317616</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737169</v>
+        <v>3.50351550673717</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776675</v>
+        <v>3.500446096776676</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781943</v>
+        <v>3.784680945781944</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567239</v>
+        <v>3.80082577856724</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712289</v>
+        <v>3.79769130871229</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966256</v>
+        <v>3.845043810966255</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046992</v>
+        <v>3.791269976046991</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412099</v>
+        <v>3.735835647412097</v>
       </c>
       <c r="C1933" t="n">
         <v>2.903141953293337</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144512</v>
+        <v>3.76264390214451</v>
       </c>
       <c r="C1934" t="n">
         <v>2.925542446615903</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.72914282290069</v>
+        <v>3.729142822900688</v>
       </c>
       <c r="C1935" t="n">
         <v>2.925614847989315</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473598</v>
+        <v>3.743216620473596</v>
       </c>
       <c r="C1936" t="n">
         <v>2.936621770464017</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978366</v>
+        <v>3.714175563978364</v>
       </c>
       <c r="C1937" t="n">
         <v>2.927058479095908</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887699</v>
+        <v>3.710903155887697</v>
       </c>
       <c r="C1938" t="n">
         <v>2.751768044136295</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.81350161240977</v>
+        <v>3.746038950675894</v>
       </c>
       <c r="C1939" t="n">
         <v>2.756335276128083</v>
@@ -46158,6 +46158,29 @@
       </c>
       <c r="G1939" t="n">
         <v>2.443677324872262</v>
+      </c>
+    </row>
+    <row r="1940">
+      <c r="A1940" s="2" t="n">
+        <v>45402</v>
+      </c>
+      <c r="B1940" t="n">
+        <v>3.811211715518479</v>
+      </c>
+      <c r="C1940" t="n">
+        <v>2.909493201863129</v>
+      </c>
+      <c r="D1940" t="n">
+        <v>-3.889272491333527</v>
+      </c>
+      <c r="E1940" t="n">
+        <v>1.200269855280925</v>
+      </c>
+      <c r="F1940" t="n">
+        <v>-0.5210965854263686</v>
+      </c>
+      <c r="G1940" t="n">
+        <v>2.902556998849497</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240420.xlsx
+++ b/tame_output/ON/bt/strategyON_20240420.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>50.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-13.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>13.9%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>37.1%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>50.5%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,20 +811,20 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-20.9%</t>
+          <t>-40.9%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-4.6%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -839,27 +839,27 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-4.5%</t>
+          <t>-7.3%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.9%</t>
+          <t>25.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-3.0%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-20.7%</t>
+          <t>-56.8%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.4%</t>
+          <t>-79.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>116.9%</t>
+          <t>117.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>136.5%</t>
+          <t>138.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.7%</t>
+          <t>94.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-705.9%</t>
+          <t>-722.5%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-57.4%</t>
+          <t>-58.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.1%</t>
+          <t>-76.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>96.9%</t>
+          <t>97.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>788.5%</t>
+          <t>781.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-550.5%</t>
+          <t>-581.5%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.7%</t>
+          <t>99.8%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-277.0%</t>
+          <t>-283.6%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-44.9%</t>
+          <t>-45.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-41.5%</t>
+          <t>-47.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-256.2%</t>
+          <t>-268.6%</t>
         </is>
       </c>
     </row>
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-26.3%</t>
+          <t>-27.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>31.3%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-161.4%</t>
+          <t>-160.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1476,22 +1476,22 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>40.1%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.2%</t>
+          <t>-16.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-155.8%</t>
+          <t>-191.9%</t>
         </is>
       </c>
     </row>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.802755682476709</v>
+        <v>-6.968320582393223</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.389167255110701</v>
+        <v>0.322941295144096</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.799118819568881</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.219147556763707</v>
+        <v>-7.38471245668022</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.2206045560047798</v>
+        <v>0.1543785960381743</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.799118819568881</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.595824567293551</v>
+        <v>-7.761389467210065</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.08019244246152102</v>
+        <v>0.0139664824949155</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.799118819568881</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.94169938927836</v>
+        <v>-8.107264289194873</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.06205792118670761</v>
+        <v>-0.1282838811533127</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.799118819568881</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.254524188523339</v>
+        <v>-8.420089088439852</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1887829208296981</v>
+        <v>-0.2550088807963031</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.799118819568881</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.551185530333537</v>
+        <v>-8.71675043025005</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3036684816245692</v>
+        <v>-0.3698944415911742</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.867861955302759</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.984534638443773</v>
+        <v>-9.150099538360285</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.4810344294030666</v>
+        <v>-0.5472603893696717</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.867861955302759</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.367536027186404</v>
+        <v>-9.533100927102916</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.634337086221703</v>
+        <v>-0.7005630461883081</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.867861955302759</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.742521353357681</v>
+        <v>-9.908086253274194</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.781759700718784</v>
+        <v>-0.8479856606853891</v>
       </c>
       <c r="F1873" t="n">
         <v>-2.242847281474037</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.10205167586168</v>
+        <v>-10.2676165757782</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.9202215264223339</v>
+        <v>-0.986447486388939</v>
       </c>
       <c r="F1874" t="n">
         <v>-2.242847281474037</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.4284517045267</v>
+        <v>-10.59401660444321</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.042865517931162</v>
+        <v>-1.109091477897767</v>
       </c>
       <c r="F1875" t="n">
         <v>-2.56924731013905</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.64760067260089</v>
+        <v>-10.81316557251741</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.127483354539072</v>
+        <v>-1.193709314505677</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.788396278213247</v>
@@ -44722,10 +44722,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.64390974764448</v>
+        <v>-10.80947464756099</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.126006984556508</v>
+        <v>-1.192232944523113</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.788396278213247</v>
@@ -44745,10 +44745,10 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.84816792297435</v>
+        <v>-11.01373282289086</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.202197057569811</v>
+        <v>-1.268423017536416</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.916035222827236</v>
@@ -44768,10 +44768,10 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.06620569460552</v>
+        <v>-11.23177059452204</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.284929611737846</v>
+        <v>-1.351155571704451</v>
       </c>
       <c r="F1879" t="n">
         <v>-3.090805990923135</v>
@@ -44791,10 +44791,10 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.99273586293807</v>
+        <v>-11.15830076285459</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.240169977577446</v>
+        <v>-1.306395937544051</v>
       </c>
       <c r="F1880" t="n">
         <v>-3.017336159255687</v>
@@ -44814,10 +44814,10 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.16786028032462</v>
+        <v>-11.33342518024113</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.295664523784546</v>
+        <v>-1.361890483751151</v>
       </c>
       <c r="F1881" t="n">
         <v>-3.19246057664223</v>
@@ -44837,10 +44837,10 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.40231237433911</v>
+        <v>-11.56787727425562</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.396664526291938</v>
+        <v>-1.462890486258543</v>
       </c>
       <c r="F1882" t="n">
         <v>-3.19246057664223</v>
@@ -44860,10 +44860,10 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.69011621887635</v>
+        <v>-11.85568111879286</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.518458254880809</v>
+        <v>-1.584684214847414</v>
       </c>
       <c r="F1883" t="n">
         <v>-3.480264421179469</v>
@@ -44883,10 +44883,10 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.91994066604017</v>
+        <v>-12.08550556595668</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.609272243907783</v>
+        <v>-1.675498203874388</v>
       </c>
       <c r="F1884" t="n">
         <v>-3.642911958249629</v>
@@ -44906,10 +44906,10 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.15196958577643</v>
+        <v>-12.31753448569295</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.699390083173173</v>
+        <v>-1.765616043139778</v>
       </c>
       <c r="F1885" t="n">
         <v>-3.704924655438052</v>
@@ -44929,10 +44929,10 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.09995407180762</v>
+        <v>-12.26551897172413</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.674593541899247</v>
+        <v>-1.740819501865852</v>
       </c>
       <c r="F1886" t="n">
         <v>-3.704924655438052</v>
@@ -44952,10 +44952,10 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.24162591353174</v>
+        <v>-12.40719081344825</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.732737505487637</v>
+        <v>-1.798963465454242</v>
       </c>
       <c r="F1887" t="n">
         <v>-3.704924655438052</v>
@@ -44975,10 +44975,10 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.34053265399102</v>
+        <v>-12.50609755390753</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.757246791506474</v>
+        <v>-1.82347275147308</v>
       </c>
       <c r="F1888" t="n">
         <v>-3.803831395897328</v>
@@ -44998,10 +44998,10 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.14138054675392</v>
+        <v>-12.30694544667043</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.690637082258319</v>
+        <v>-1.756863042224924</v>
       </c>
       <c r="F1889" t="n">
         <v>-3.638508869947514</v>
@@ -45021,10 +45021,10 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.91553539403451</v>
+        <v>-12.08110029395102</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.590719948134346</v>
+        <v>-1.65694590810095</v>
       </c>
       <c r="F1890" t="n">
         <v>-3.596582194360351</v>
@@ -45044,10 +45044,10 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.62926058171181</v>
+        <v>-11.79482548162832</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.475070878649209</v>
+        <v>-1.541296838615813</v>
       </c>
       <c r="F1891" t="n">
         <v>-3.596582194360351</v>
@@ -45067,10 +45067,10 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.6821558697561</v>
+        <v>-11.84772076967261</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.493595219704815</v>
+        <v>-1.559821179671419</v>
       </c>
       <c r="F1892" t="n">
         <v>-3.591626848271904</v>
@@ -45090,10 +45090,10 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.39824713882735</v>
+        <v>-11.56381203874386</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.37429802309468</v>
+        <v>-1.440523983061284</v>
       </c>
       <c r="F1893" t="n">
         <v>-3.591626848271904</v>
@@ -45113,10 +45113,10 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.28282621468925</v>
+        <v>-11.44839111460576</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.337866915833306</v>
+        <v>-1.40409287579991</v>
       </c>
       <c r="F1894" t="n">
         <v>-3.476205924133809</v>
@@ -45136,10 +45136,10 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.01898934748518</v>
+        <v>-11.18455424740169</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.242215650264586</v>
+        <v>-1.30844161023119</v>
       </c>
       <c r="F1895" t="n">
         <v>-3.476205924133809</v>
@@ -45159,10 +45159,10 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.75174754661679</v>
+        <v>-10.9173124465333</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.137153490416601</v>
+        <v>-1.203379450383205</v>
       </c>
       <c r="F1896" t="n">
         <v>-3.476205924133809</v>
@@ -45176,16 +45176,16 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781944</v>
+        <v>3.784680945781943</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.62844161813857</v>
+        <v>-10.79400651805508</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.088131433998774</v>
+        <v>-1.154357393965378</v>
       </c>
       <c r="F1897" t="n">
         <v>-3.386788253006246</v>
@@ -45199,16 +45199,16 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.80082577856724</v>
+        <v>3.800825778567239</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.60448807716261</v>
+        <v>-10.77005297707912</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.077881511462897</v>
+        <v>-1.144107471429501</v>
       </c>
       <c r="F1898" t="n">
         <v>-3.362834712030288</v>
@@ -45222,16 +45222,16 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487769</v>
+        <v>3.789307536487768</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.34042813883981</v>
+        <v>-10.50599303875632</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.9855178522955299</v>
+        <v>-1.051743812262135</v>
       </c>
       <c r="F1899" t="n">
         <v>-3.098774773707492</v>
@@ -45251,10 +45251,10 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.633348515334974</v>
+        <v>-9.798913415251485</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.7054730365538964</v>
+        <v>-0.7716989965205006</v>
       </c>
       <c r="F1900" t="n">
         <v>-3.098774773707492</v>
@@ -45268,16 +45268,16 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858725</v>
+        <v>3.839370871858724</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.593164216968784</v>
+        <v>-9.758729116885295</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.6890556933195788</v>
+        <v>-0.755281653286183</v>
       </c>
       <c r="F1901" t="n">
         <v>-3.058590475341301</v>
@@ -45291,16 +45291,16 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096471</v>
+        <v>3.85615817609647</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.51309442143098</v>
+        <v>-9.678659321347491</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.6576609538836999</v>
+        <v>-0.7238869138503041</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.978520679803497</v>
@@ -45314,16 +45314,16 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761807</v>
+        <v>3.787326853761806</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.279613199201382</v>
+        <v>-9.445178099117893</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.5563440361540084</v>
+        <v>-0.622569996120613</v>
       </c>
       <c r="F1903" t="n">
         <v>-2.745039457573899</v>
@@ -45337,16 +45337,16 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255785</v>
+        <v>3.801633547255783</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.099904669057508</v>
+        <v>-9.265469568974019</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.4873528344094185</v>
+        <v>-0.5535787943760226</v>
       </c>
       <c r="F1904" t="n">
         <v>-2.687867953411203</v>
@@ -45360,16 +45360,16 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860425</v>
+        <v>3.763178672860423</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.967629195426621</v>
+        <v>-9.133194095343132</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.4390751582100365</v>
+        <v>-0.5053011181766407</v>
       </c>
       <c r="F1905" t="n">
         <v>-2.555592479780316</v>
@@ -45383,16 +45383,16 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.78471521857595</v>
+        <v>3.784715218575948</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.777029520753468</v>
+        <v>-8.942594420669979</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.3600202276531381</v>
+        <v>-0.4262461876197428</v>
       </c>
       <c r="F1906" t="n">
         <v>-2.364992805107164</v>
@@ -45406,16 +45406,16 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430985</v>
+        <v>3.753878996430983</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.528029722069887</v>
+        <v>-8.693594621986398</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.2475139669560469</v>
+        <v>-0.3137399269226515</v>
       </c>
       <c r="F1907" t="n">
         <v>-2.364992805107164</v>
@@ -45429,16 +45429,16 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077642</v>
+        <v>3.69292828007764</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.633619711842991</v>
+        <v>-8.799184611759502</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4177258924645075</v>
+        <v>-0.4839518524311117</v>
       </c>
       <c r="F1908" t="n">
         <v>-2.470582794880268</v>
@@ -45452,16 +45452,16 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.7704190084579</v>
+        <v>3.770419008457898</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.652354613961588</v>
+        <v>-8.817919513878099</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.3766755114348599</v>
+        <v>-0.4429014714014645</v>
       </c>
       <c r="F1909" t="n">
         <v>-2.470582794880268</v>
@@ -45475,16 +45475,16 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180808</v>
+        <v>3.760330111180807</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.504414572553989</v>
+        <v>-8.6699794724705</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.4373784175599877</v>
+        <v>-0.5036043775265924</v>
       </c>
       <c r="F1910" t="n">
         <v>-2.45026187897171</v>
@@ -45498,16 +45498,16 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879201</v>
+        <v>3.723562653879199</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.377522166118919</v>
+        <v>-8.543087066035429</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.3953354412394381</v>
+        <v>-0.4615614012060423</v>
       </c>
       <c r="F1911" t="n">
         <v>-2.323369472536641</v>
@@ -45521,16 +45521,16 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568105</v>
+        <v>3.729966140568103</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.333973759348227</v>
+        <v>-8.499538659264738</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.3848766906262546</v>
+        <v>-0.4511026505928588</v>
       </c>
       <c r="F1912" t="n">
         <v>-2.323369472536641</v>
@@ -45544,16 +45544,16 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963416</v>
+        <v>3.782918957963414</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.091825365894369</v>
+        <v>-8.25739026581088</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.2735549788635683</v>
+        <v>-0.3397809388301725</v>
       </c>
       <c r="F1913" t="n">
         <v>-2.323369472536641</v>
@@ -45567,16 +45567,16 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192812</v>
+        <v>3.82854791119281</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.028595994126022</v>
+        <v>-8.194160894042533</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.2537311096970343</v>
+        <v>-0.3199570696636385</v>
       </c>
       <c r="F1914" t="n">
         <v>-2.323369472536641</v>
@@ -45590,16 +45590,16 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262042</v>
+        <v>3.82804935326204</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.842108301749016</v>
+        <v>-8.007673201665526</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.1816379387356548</v>
+        <v>-0.2478638987022594</v>
       </c>
       <c r="F1915" t="n">
         <v>-2.136881780159634</v>
@@ -45613,16 +45613,16 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389904</v>
+        <v>3.812450103389902</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.820959102845572</v>
+        <v>-7.986524002762082</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.1654772809369525</v>
+        <v>-0.2317032409035567</v>
       </c>
       <c r="F1916" t="n">
         <v>-2.115732581256191</v>
@@ -45636,16 +45636,16 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788089</v>
+        <v>3.748324832788088</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.577193660862128</v>
+        <v>-7.742758560778638</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.07219039579652398</v>
+        <v>-0.1384163557631282</v>
       </c>
       <c r="F1917" t="n">
         <v>-2.115732581256191</v>
@@ -45659,16 +45659,16 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527521</v>
+        <v>3.82430765752752</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.313165593668868</v>
+        <v>-7.478730493585378</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.03554514500079575</v>
+        <v>-0.03068081496580843</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.913867182440237</v>
@@ -45682,16 +45682,16 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.82635139874918</v>
+        <v>3.826351398749178</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.063315199719794</v>
+        <v>-7.228880099636304</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.1282273775641278</v>
+        <v>0.06200141759752364</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.913867182440237</v>
@@ -45705,16 +45705,16 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481493</v>
+        <v>3.835954411481492</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.759747710715815</v>
+        <v>-6.925312610632325</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.253253496686368</v>
+        <v>0.1870275367197638</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.913867182440237</v>
@@ -45728,16 +45728,16 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862982</v>
+        <v>3.780930335862981</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.686267801863801</v>
+        <v>-6.851832701780311</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.2959729662817274</v>
+        <v>0.2297470063151228</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.840387273588223</v>
@@ -45751,16 +45751,16 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102777</v>
+        <v>3.773761647102775</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.461234802194978</v>
+        <v>-6.626799702111488</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.3850066437655535</v>
+        <v>0.3187806837989493</v>
       </c>
       <c r="F1922" t="n">
         <v>-1.6153542739194</v>
@@ -45774,16 +45774,16 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353069</v>
+        <v>3.764614304353067</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.246600424558571</v>
+        <v>-6.412165324475081</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.4755551958744335</v>
+        <v>0.4093292359078293</v>
       </c>
       <c r="F1923" t="n">
         <v>-1.400719896282993</v>
@@ -45797,16 +45797,16 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544777</v>
+        <v>3.798811195544776</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.98000006758422</v>
+        <v>-6.14556496750073</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.5633895974479701</v>
+        <v>0.4971636374813655</v>
       </c>
       <c r="F1924" t="n">
         <v>-1.400719896282993</v>
@@ -45820,16 +45820,16 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.79769130871229</v>
+        <v>3.797691308712287</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.739569570779359</v>
+        <v>-5.905134470695869</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.6613048727947914</v>
+        <v>0.5950789128281873</v>
       </c>
       <c r="F1925" t="n">
         <v>-1.160289399478133</v>
@@ -45843,16 +45843,16 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82158993383768</v>
+        <v>3.821589933837679</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.496778763129914</v>
+        <v>-5.806725264215167</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7623505096893899</v>
+        <v>0.6383719092552882</v>
       </c>
       <c r="F1926" t="n">
         <v>-1.160289399478133</v>
@@ -45866,16 +45866,16 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349962</v>
+        <v>3.82232342234996</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.257173671522825</v>
+        <v>-5.567120172608077</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8588711302495655</v>
+        <v>0.7348925298154643</v>
       </c>
       <c r="F1927" t="n">
         <v>-1.093241451809638</v>
@@ -45889,16 +45889,16 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972335</v>
+        <v>3.848613050972333</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.014518083099661</v>
+        <v>-5.324464584184914</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9529314368388242</v>
+        <v>0.8289528364047229</v>
       </c>
       <c r="F1928" t="n">
         <v>-1.093241451809638</v>
@@ -45912,16 +45912,16 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145936</v>
+        <v>3.818665376145934</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.794497285062651</v>
+        <v>-5.104443786147903</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.042518793064243</v>
+        <v>0.9185401926301413</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.9520216067416583</v>
@@ -45935,16 +45935,16 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009947</v>
+        <v>3.843270952009945</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.595248655157842</v>
+        <v>-4.905195156243094</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.13811242782799</v>
+        <v>1.014133827393888</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.9520216067416583</v>
@@ -45958,16 +45958,16 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966255</v>
+        <v>3.845043810966254</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.435733551638472</v>
+        <v>-4.745680052723724</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.203064313676039</v>
+        <v>1.079085713241938</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.7925065032222883</v>
@@ -45981,16 +45981,16 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046991</v>
+        <v>3.79126997604699</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.291061406538734</v>
+        <v>-4.601007907623987</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.271021274277374</v>
+        <v>1.147042673843273</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.647834358122551</v>
@@ -46004,16 +46004,16 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412097</v>
+        <v>3.735835647412095</v>
       </c>
       <c r="C1933" t="n">
         <v>2.903141953293337</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.273291947607778</v>
+        <v>-4.583238448693031</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.193468749936478</v>
+        <v>1.069490149502377</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.6300648991915954</v>
@@ -46027,16 +46027,16 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.76264390214451</v>
+        <v>3.762643902144508</v>
       </c>
       <c r="C1934" t="n">
         <v>2.925542446615903</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.186492449828769</v>
+        <v>-4.496438950914022</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.250589042370648</v>
+        <v>1.126610441936547</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.6300648991915954</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900688</v>
+        <v>3.729142822900687</v>
       </c>
       <c r="C1935" t="n">
         <v>2.925614847989315</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.086799835099757</v>
+        <v>-4.39674633618501</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.290538489635665</v>
+        <v>1.166559889201564</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.5303722844625836</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473596</v>
+        <v>3.743216620473595</v>
       </c>
       <c r="C1936" t="n">
         <v>2.936621770464017</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.155170021423768</v>
+        <v>-4.46511652250902</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.274197337580763</v>
+        <v>1.150218737146661</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.5210965854263686</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978364</v>
+        <v>3.714175563978363</v>
       </c>
       <c r="C1937" t="n">
         <v>2.927058479095908</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.033753591797291</v>
+        <v>-4.343700092882544</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.313200618063245</v>
+        <v>1.189222017629143</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.5210965854263686</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887697</v>
+        <v>3.710903155887696</v>
       </c>
       <c r="C1938" t="n">
         <v>2.751768044136295</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.064746751125996</v>
+        <v>-4.374693252211249</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.125512919372149</v>
+        <v>1.001534318938048</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.5210965854263686</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675894</v>
+        <v>3.746038950675892</v>
       </c>
       <c r="C1939" t="n">
         <v>2.756335276128083</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.889272491333527</v>
+        <v>-4.199218992418779</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.200269855280925</v>
+        <v>1.076291254846824</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.5210965854263686</v>
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.811211715518479</v>
+        <v>3.419923390934126</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.909493201863129</v>
+        <v>2.54836950031383</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.889272491333527</v>
+        <v>-4.199218992418779</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.200269855280925</v>
+        <v>1.076291254846824</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.5210965854263686</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.902556998849497</v>
+        <v>2.541433297300197</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240420.xlsx
+++ b/tame_output/ON/bt/strategyON_20240420.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-13.0%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>53.3%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>37.1%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,20 +811,20 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-40.9%</t>
+          <t>-20.9%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -839,27 +839,27 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-4.5%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>25.1%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-3.0%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-56.8%</t>
+          <t>-20.4%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.8%</t>
+          <t>-78.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>117.3%</t>
+          <t>117.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>138.1%</t>
+          <t>136.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.8%</t>
+          <t>95.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-722.5%</t>
+          <t>-706.0%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-58.0%</t>
+          <t>-57.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.4%</t>
+          <t>-74.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>97.3%</t>
+          <t>97.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>781.2%</t>
+          <t>788.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-2.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-581.5%</t>
+          <t>-550.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.8%</t>
+          <t>99.7%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-283.6%</t>
+          <t>-277.0%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-45.4%</t>
+          <t>-44.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-47.7%</t>
+          <t>-41.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-268.6%</t>
+          <t>-256.2%</t>
         </is>
       </c>
     </row>
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-27.2%</t>
+          <t>-26.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-160.2%</t>
+          <t>-161.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>48.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1476,22 +1476,22 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>40.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.0%</t>
+          <t>-16.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-191.9%</t>
+          <t>-155.5%</t>
         </is>
       </c>
     </row>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.761389467210065</v>
+        <v>-7.59703422617594</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.0139664824949155</v>
+        <v>0.0797085789085652</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.799118819568881</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.107264289194873</v>
+        <v>-7.942909048160748</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.1282838811533127</v>
+        <v>-0.06254178473966299</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.799118819568881</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.420089088439852</v>
+        <v>-8.255733847405727</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.2550088807963031</v>
+        <v>-0.1892667843826534</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.799118819568881</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.71675043025005</v>
+        <v>-8.552395189215925</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3698944415911742</v>
+        <v>-0.3041523451775245</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.867861955302759</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.150099538360285</v>
+        <v>-8.985744297326161</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.5472603893696717</v>
+        <v>-0.4815182929560216</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.867861955302759</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.533100927102916</v>
+        <v>-9.368745686068792</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.7005630461883081</v>
+        <v>-0.6348209497746584</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.867861955302759</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.908086253274194</v>
+        <v>-9.743731012240069</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.8479856606853891</v>
+        <v>-0.7822435642717389</v>
       </c>
       <c r="F1873" t="n">
         <v>-2.242847281474037</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.2676165757782</v>
+        <v>-10.10326133474407</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.986447486388939</v>
+        <v>-0.9207053899752893</v>
       </c>
       <c r="F1874" t="n">
         <v>-2.242847281474037</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.59401660444321</v>
+        <v>-10.42966136340908</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.109091477897767</v>
+        <v>-1.043349381484117</v>
       </c>
       <c r="F1875" t="n">
         <v>-2.56924731013905</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.81316557251741</v>
+        <v>-10.64881033148328</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.193709314505677</v>
+        <v>-1.127967218092027</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.788396278213247</v>
@@ -44716,16 +44716,16 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407493</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.80947464756099</v>
+        <v>-10.64511940652687</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.192232944523113</v>
+        <v>-1.126490848109463</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.788396278213247</v>
@@ -44739,16 +44739,16 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611696</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-11.01373282289086</v>
+        <v>-10.84937758185673</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.268423017536416</v>
+        <v>-1.202680921122766</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.916035222827236</v>
@@ -44768,10 +44768,10 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.23177059452204</v>
+        <v>-11.06741535348791</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.351155571704451</v>
+        <v>-1.285413475290801</v>
       </c>
       <c r="F1879" t="n">
         <v>-3.090805990923135</v>
@@ -44785,16 +44785,16 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910628</v>
+        <v>3.499968163910629</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-11.15830076285459</v>
+        <v>-10.99394552182046</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.306395937544051</v>
+        <v>-1.2406538411304</v>
       </c>
       <c r="F1880" t="n">
         <v>-3.017336159255687</v>
@@ -44808,16 +44808,16 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078595</v>
+        <v>3.490055666078596</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.33342518024113</v>
+        <v>-11.16906993920701</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.361890483751151</v>
+        <v>-1.296148387337501</v>
       </c>
       <c r="F1881" t="n">
         <v>-3.19246057664223</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880267</v>
+        <v>3.485875018880268</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.56787727425562</v>
+        <v>-11.4035220332215</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.462890486258543</v>
+        <v>-1.397148389844892</v>
       </c>
       <c r="F1882" t="n">
         <v>-3.19246057664223</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234391</v>
+        <v>3.480688917234392</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.85568111879286</v>
+        <v>-11.69132587775873</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.584684214847414</v>
+        <v>-1.518942118433765</v>
       </c>
       <c r="F1883" t="n">
         <v>-3.480264421179469</v>
@@ -44877,16 +44877,16 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860581</v>
+        <v>3.493712438860582</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-12.08550556595668</v>
+        <v>-11.92115032492256</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.675498203874388</v>
+        <v>-1.609756107460738</v>
       </c>
       <c r="F1884" t="n">
         <v>-3.642911958249629</v>
@@ -44900,16 +44900,16 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767395</v>
+        <v>3.492098065767396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.31753448569295</v>
+        <v>-12.15317924465882</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.765616043139778</v>
+        <v>-1.699873946726128</v>
       </c>
       <c r="F1885" t="n">
         <v>-3.704924655438052</v>
@@ -44923,16 +44923,16 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.57367044979254</v>
+        <v>3.573670449792541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.26551897172413</v>
+        <v>-12.10116373069001</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.740819501865852</v>
+        <v>-1.675077405452202</v>
       </c>
       <c r="F1886" t="n">
         <v>-3.704924655438052</v>
@@ -44946,16 +44946,16 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628917</v>
+        <v>3.600034689628918</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.40719081344825</v>
+        <v>-12.24283557241413</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.798963465454242</v>
+        <v>-1.733221369040592</v>
       </c>
       <c r="F1887" t="n">
         <v>-3.704924655438052</v>
@@ -44969,16 +44969,16 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410715</v>
+        <v>3.691568158410716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.50609755390753</v>
+        <v>-12.3417423128734</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.82347275147308</v>
+        <v>-1.75773065505943</v>
       </c>
       <c r="F1888" t="n">
         <v>-3.803831395897328</v>
@@ -44992,16 +44992,16 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240575</v>
+        <v>3.676837974240576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.30694544667043</v>
+        <v>-12.1425902056363</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.756863042224924</v>
+        <v>-1.691120945811273</v>
       </c>
       <c r="F1889" t="n">
         <v>-3.638508869947514</v>
@@ -45015,16 +45015,16 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085278</v>
+        <v>3.685157806085279</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-12.08110029395102</v>
+        <v>-11.91674505291689</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.65694590810095</v>
+        <v>-1.5912038116873</v>
       </c>
       <c r="F1890" t="n">
         <v>-3.596582194360351</v>
@@ -45038,16 +45038,16 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282098</v>
+        <v>3.684840248282099</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.79482548162832</v>
+        <v>-11.6304702405942</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.541296838615813</v>
+        <v>-1.475554742202164</v>
       </c>
       <c r="F1891" t="n">
         <v>-3.596582194360351</v>
@@ -45067,10 +45067,10 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.84772076967261</v>
+        <v>-11.68336552863849</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.559821179671419</v>
+        <v>-1.494079083257771</v>
       </c>
       <c r="F1892" t="n">
         <v>-3.591626848271904</v>
@@ -45084,16 +45084,16 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081564</v>
+        <v>3.768948099081565</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.56381203874386</v>
+        <v>-11.39945679770974</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.440523983061284</v>
+        <v>-1.374781886647635</v>
       </c>
       <c r="F1893" t="n">
         <v>-3.591626848271904</v>
@@ -45107,16 +45107,16 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425323</v>
+        <v>3.728574354425324</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.44839111460576</v>
+        <v>-11.28403587357164</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.40409287579991</v>
+        <v>-1.338350779386261</v>
       </c>
       <c r="F1894" t="n">
         <v>-3.476205924133809</v>
@@ -45130,16 +45130,16 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702407</v>
+        <v>3.747699084702408</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.18455424740169</v>
+        <v>-11.02019900636757</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.30844161023119</v>
+        <v>-1.242699513817541</v>
       </c>
       <c r="F1895" t="n">
         <v>-3.476205924133809</v>
@@ -45153,16 +45153,16 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906223</v>
+        <v>3.766313503906224</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.9173124465333</v>
+        <v>-10.75295720549917</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.203379450383205</v>
+        <v>-1.137637353969555</v>
       </c>
       <c r="F1896" t="n">
         <v>-3.476205924133809</v>
@@ -45176,16 +45176,16 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781943</v>
+        <v>3.784680945781945</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.79400651805508</v>
+        <v>-10.62965127702095</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.154357393965378</v>
+        <v>-1.088615297551728</v>
       </c>
       <c r="F1897" t="n">
         <v>-3.386788253006246</v>
@@ -45199,16 +45199,16 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567239</v>
+        <v>3.800825778567241</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.77005297707912</v>
+        <v>-10.605697736045</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.144107471429501</v>
+        <v>-1.078365375015852</v>
       </c>
       <c r="F1898" t="n">
         <v>-3.362834712030288</v>
@@ -45222,16 +45222,16 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487768</v>
+        <v>3.78930753648777</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.50599303875632</v>
+        <v>-10.3416377977222</v>
       </c>
       <c r="E1899" t="n">
-        <v>-1.051743812262135</v>
+        <v>-0.9860017158484853</v>
       </c>
       <c r="F1899" t="n">
         <v>-3.098774773707492</v>
@@ -45245,16 +45245,16 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309722</v>
+        <v>3.833249172309723</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.798913415251485</v>
+        <v>-9.634558174217362</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.7716989965205006</v>
+        <v>-0.7059569001068513</v>
       </c>
       <c r="F1900" t="n">
         <v>-3.098774773707492</v>
@@ -45268,16 +45268,16 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858724</v>
+        <v>3.839370871858726</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.758729116885295</v>
+        <v>-9.594373875851172</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.755281653286183</v>
+        <v>-0.6895395568725338</v>
       </c>
       <c r="F1901" t="n">
         <v>-3.058590475341301</v>
@@ -45291,16 +45291,16 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.85615817609647</v>
+        <v>3.856158176096471</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.678659321347491</v>
+        <v>-9.514304080313368</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.7238869138503041</v>
+        <v>-0.6581448174366553</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.978520679803497</v>
@@ -45314,16 +45314,16 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761806</v>
+        <v>3.787326853761807</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.445178099117893</v>
+        <v>-9.28082285808377</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.622569996120613</v>
+        <v>-0.5568278997069638</v>
       </c>
       <c r="F1903" t="n">
         <v>-2.745039457573899</v>
@@ -45337,16 +45337,16 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255783</v>
+        <v>3.801633547255785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.265469568974019</v>
+        <v>-9.101114327939896</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.5535787943760226</v>
+        <v>-0.4878366979623734</v>
       </c>
       <c r="F1904" t="n">
         <v>-2.687867953411203</v>
@@ -45360,16 +45360,16 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860423</v>
+        <v>3.763178672860425</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-9.133194095343132</v>
+        <v>-8.968838854309009</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.5053011181766407</v>
+        <v>-0.4395590217629914</v>
       </c>
       <c r="F1905" t="n">
         <v>-2.555592479780316</v>
@@ -45383,16 +45383,16 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575948</v>
+        <v>3.78471521857595</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.942594420669979</v>
+        <v>-8.778239179635856</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.4262461876197428</v>
+        <v>-0.3605040912060935</v>
       </c>
       <c r="F1906" t="n">
         <v>-2.364992805107164</v>
@@ -45406,16 +45406,16 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430983</v>
+        <v>3.753878996430985</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.693594621986398</v>
+        <v>-8.529239380952275</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.3137399269226515</v>
+        <v>-0.2479978305090023</v>
       </c>
       <c r="F1907" t="n">
         <v>-2.364992805107164</v>
@@ -45429,16 +45429,16 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.69292828007764</v>
+        <v>3.692928280077642</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.799184611759502</v>
+        <v>-8.634829370725379</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4839518524311117</v>
+        <v>-0.4182097560174629</v>
       </c>
       <c r="F1908" t="n">
         <v>-2.470582794880268</v>
@@ -45452,16 +45452,16 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457898</v>
+        <v>3.7704190084579</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.817919513878099</v>
+        <v>-8.653564272843976</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.4429014714014645</v>
+        <v>-0.3771593749878153</v>
       </c>
       <c r="F1909" t="n">
         <v>-2.470582794880268</v>
@@ -45475,16 +45475,16 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180807</v>
+        <v>3.760330111180808</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.6699794724705</v>
+        <v>-8.505624231436377</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.5036043775265924</v>
+        <v>-0.4378622811129431</v>
       </c>
       <c r="F1910" t="n">
         <v>-2.45026187897171</v>
@@ -45498,16 +45498,16 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879199</v>
+        <v>3.723562653879201</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.543087066035429</v>
+        <v>-8.378731825001307</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.4615614012060423</v>
+        <v>-0.395819304792393</v>
       </c>
       <c r="F1911" t="n">
         <v>-2.323369472536641</v>
@@ -45521,16 +45521,16 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568103</v>
+        <v>3.729966140568105</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.499538659264738</v>
+        <v>-8.335183418230615</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.4511026505928588</v>
+        <v>-0.3853605541792096</v>
       </c>
       <c r="F1912" t="n">
         <v>-2.323369472536641</v>
@@ -45544,16 +45544,16 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963414</v>
+        <v>3.782918957963416</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.25739026581088</v>
+        <v>-8.093035024776757</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.3397809388301725</v>
+        <v>-0.2740388424165232</v>
       </c>
       <c r="F1913" t="n">
         <v>-2.323369472536641</v>
@@ -45567,16 +45567,16 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.82854791119281</v>
+        <v>3.828547911192812</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.194160894042533</v>
+        <v>-8.02980565300841</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.3199570696636385</v>
+        <v>-0.2542149732499892</v>
       </c>
       <c r="F1914" t="n">
         <v>-2.323369472536641</v>
@@ -45590,16 +45590,16 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.82804935326204</v>
+        <v>3.828049353262042</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-8.007673201665526</v>
+        <v>-7.843317960631404</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.2478638987022594</v>
+        <v>-0.1821218022886102</v>
       </c>
       <c r="F1915" t="n">
         <v>-2.136881780159634</v>
@@ -45613,16 +45613,16 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389902</v>
+        <v>3.812450103389904</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.986524002762082</v>
+        <v>-7.82216876172796</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.2317032409035567</v>
+        <v>-0.1659611444899074</v>
       </c>
       <c r="F1916" t="n">
         <v>-2.115732581256191</v>
@@ -45636,16 +45636,16 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788088</v>
+        <v>3.748324832788089</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.742758560778638</v>
+        <v>-7.578403319744516</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.1384163557631282</v>
+        <v>-0.07267425934947935</v>
       </c>
       <c r="F1917" t="n">
         <v>-2.115732581256191</v>
@@ -45659,16 +45659,16 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.82430765752752</v>
+        <v>3.824307657527521</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.478730493585378</v>
+        <v>-7.314375252551256</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.03068081496580843</v>
+        <v>0.03506128144784082</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.913867182440237</v>
@@ -45682,16 +45682,16 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749178</v>
+        <v>3.82635139874918</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.228880099636304</v>
+        <v>-7.064524858602182</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.06200141759752364</v>
+        <v>0.1277435140111725</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.913867182440237</v>
@@ -45705,16 +45705,16 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481492</v>
+        <v>3.835954411481493</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.925312610632325</v>
+        <v>-6.760957369598203</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.1870275367197638</v>
+        <v>0.2527696331334131</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.913867182440237</v>
@@ -45728,16 +45728,16 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862981</v>
+        <v>3.780930335862982</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.851832701780311</v>
+        <v>-6.687477460746189</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.2297470063151228</v>
+        <v>0.295489102728772</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.840387273588223</v>
@@ -45751,16 +45751,16 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102775</v>
+        <v>3.773761647102777</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.626799702111488</v>
+        <v>-6.462444461077366</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.3187806837989493</v>
+        <v>0.3845227802125981</v>
       </c>
       <c r="F1922" t="n">
         <v>-1.6153542739194</v>
@@ -45774,16 +45774,16 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353067</v>
+        <v>3.764614304353069</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.412165324475081</v>
+        <v>-6.247810083440959</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.4093292359078293</v>
+        <v>0.4750713323214781</v>
       </c>
       <c r="F1923" t="n">
         <v>-1.400719896282993</v>
@@ -45797,16 +45797,16 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544776</v>
+        <v>3.798811195544777</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.14556496750073</v>
+        <v>-5.981209726466608</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4971636374813655</v>
+        <v>0.5629057338950147</v>
       </c>
       <c r="F1924" t="n">
         <v>-1.400719896282993</v>
@@ -45820,16 +45820,16 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712287</v>
+        <v>3.797691308712289</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.905134470695869</v>
+        <v>-5.740779229661747</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5950789128281873</v>
+        <v>0.6608210092418361</v>
       </c>
       <c r="F1925" t="n">
         <v>-1.160289399478133</v>
@@ -45843,16 +45843,16 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837679</v>
+        <v>3.82158993383768</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.806725264215167</v>
+        <v>-5.497988422012302</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6383719092552882</v>
+        <v>0.7618666461364345</v>
       </c>
       <c r="F1926" t="n">
         <v>-1.160289399478133</v>
@@ -45866,16 +45866,16 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.82232342234996</v>
+        <v>3.822323422349962</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.567120172608077</v>
+        <v>-5.258383330405213</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7348925298154643</v>
+        <v>0.8583872666966101</v>
       </c>
       <c r="F1927" t="n">
         <v>-1.093241451809638</v>
@@ -45889,16 +45889,16 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972333</v>
+        <v>3.848613050972335</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.324464584184914</v>
+        <v>-5.015727741982049</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8289528364047229</v>
+        <v>0.9524475732858693</v>
       </c>
       <c r="F1928" t="n">
         <v>-1.093241451809638</v>
@@ -45912,16 +45912,16 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145934</v>
+        <v>3.818665376145936</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.104443786147903</v>
+        <v>-4.795706943945039</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9185401926301413</v>
+        <v>1.042034929511288</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.9520216067416583</v>
@@ -45935,16 +45935,16 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009945</v>
+        <v>3.843270952009947</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.905195156243094</v>
+        <v>-4.59645831404023</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.014133827393888</v>
+        <v>1.137628564275035</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.9520216067416583</v>
@@ -45958,16 +45958,16 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966254</v>
+        <v>3.845043810966256</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.745680052723724</v>
+        <v>-4.43694321052086</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.079085713241938</v>
+        <v>1.202580450123084</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.7925065032222883</v>
@@ -45981,16 +45981,16 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.79126997604699</v>
+        <v>3.791269976046992</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.601007907623987</v>
+        <v>-4.292271065421122</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.147042673843273</v>
+        <v>1.270537410724419</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.647834358122551</v>
@@ -46004,16 +46004,16 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412095</v>
+        <v>3.735835647412099</v>
       </c>
       <c r="C1933" t="n">
         <v>2.903141953293337</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.583238448693031</v>
+        <v>-4.274501606490166</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.069490149502377</v>
+        <v>1.192984886383523</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.6300648991915954</v>
@@ -46027,16 +46027,16 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144508</v>
+        <v>3.762643902144512</v>
       </c>
       <c r="C1934" t="n">
         <v>2.925542446615903</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.496438950914022</v>
+        <v>-4.187702108711157</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.126610441936547</v>
+        <v>1.250105178817693</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.6300648991915954</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900687</v>
+        <v>3.72914282290069</v>
       </c>
       <c r="C1935" t="n">
         <v>2.925614847989315</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.39674633618501</v>
+        <v>-4.088009493982145</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.166559889201564</v>
+        <v>1.29005462608271</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.5303722844625836</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473595</v>
+        <v>3.743216620473598</v>
       </c>
       <c r="C1936" t="n">
         <v>2.936621770464017</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.46511652250902</v>
+        <v>-4.156379680306156</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.150218737146661</v>
+        <v>1.273713474027808</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.5210965854263686</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978363</v>
+        <v>3.714175563978366</v>
       </c>
       <c r="C1937" t="n">
         <v>2.927058479095908</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.343700092882544</v>
+        <v>-4.034963250679679</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.189222017629143</v>
+        <v>1.31271675451029</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.5210965854263686</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887696</v>
+        <v>3.710903155887699</v>
       </c>
       <c r="C1938" t="n">
         <v>2.751768044136295</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.374693252211249</v>
+        <v>-4.065956410008384</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.001534318938048</v>
+        <v>1.125029055819194</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.5210965854263686</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675892</v>
+        <v>3.746038950675896</v>
       </c>
       <c r="C1939" t="n">
         <v>2.756335276128083</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.199218992418779</v>
+        <v>-3.890482150215915</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.076291254846824</v>
+        <v>1.19978599172797</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.5210965854263686</v>
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.419923390934126</v>
+        <v>3.814168122586401</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.54836950031383</v>
+        <v>2.912647637581391</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.199218992418779</v>
+        <v>-3.890482150215915</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.076291254846824</v>
+        <v>1.19978599172797</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.5210965854263686</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.541433297300197</v>
+        <v>2.905711434567759</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240420.xlsx
+++ b/tame_output/ON/bt/strategyON_20240420.xlsx
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>60.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-4.5%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-20.4%</t>
+          <t>-36.0%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.4%</t>
+          <t>-78.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>117.0%</t>
+          <t>117.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>136.7%</t>
+          <t>136.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.2%</t>
+          <t>-74.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>97.0%</t>
+          <t>97.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-550.6%</t>
+          <t>-562.1%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>5.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-256.2%</t>
+          <t>-260.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>40.1%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>33.5%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-155.5%</t>
+          <t>-201.7%</t>
         </is>
       </c>
     </row>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097818</v>
+        <v>3.341378723097819</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407493</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611696</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910629</v>
+        <v>3.499968163910628</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078596</v>
+        <v>3.490055666078595</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880268</v>
+        <v>3.485875018880267</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234392</v>
+        <v>3.480688917234391</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860582</v>
+        <v>3.493712438860581</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767396</v>
+        <v>3.492098065767395</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792541</v>
+        <v>3.57367044979254</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628918</v>
+        <v>3.600034689628917</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410716</v>
+        <v>3.691568158410715</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240576</v>
+        <v>3.676837974240575</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085279</v>
+        <v>3.685157806085278</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282099</v>
+        <v>3.684840248282098</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081565</v>
+        <v>3.768948099081564</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425324</v>
+        <v>3.728574354425323</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702408</v>
+        <v>3.747699084702407</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906224</v>
+        <v>3.766313503906223</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781945</v>
+        <v>3.784680945781943</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567241</v>
+        <v>3.800825778567239</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.78930753648777</v>
+        <v>3.789307536487768</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309723</v>
+        <v>3.833249172309722</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858726</v>
+        <v>3.839370871858724</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096471</v>
+        <v>3.85615817609647</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761807</v>
+        <v>3.787326853761806</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255785</v>
+        <v>3.801633547255783</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860425</v>
+        <v>3.763178672860423</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.78471521857595</v>
+        <v>3.784715218575948</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430985</v>
+        <v>3.753878996430983</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077642</v>
+        <v>3.69292828007764</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.7704190084579</v>
+        <v>3.770419008457898</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180808</v>
+        <v>3.760330111180807</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879201</v>
+        <v>3.723562653879199</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568105</v>
+        <v>3.729966140568103</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963416</v>
+        <v>3.782918957963414</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192812</v>
+        <v>3.82854791119281</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262042</v>
+        <v>3.82804935326204</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389904</v>
+        <v>3.812450103389902</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788089</v>
+        <v>3.748324832788088</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527521</v>
+        <v>3.82430765752752</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.82635139874918</v>
+        <v>3.826351398749178</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481493</v>
+        <v>3.835954411481492</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862982</v>
+        <v>3.780930335862981</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102777</v>
+        <v>3.773761647102775</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353069</v>
+        <v>3.764614304353067</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544777</v>
+        <v>3.798811195544776</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712289</v>
+        <v>3.797691308712287</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82158993383768</v>
+        <v>3.821589933837679</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349962</v>
+        <v>3.82232342234996</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972335</v>
+        <v>3.848613050972333</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145936</v>
+        <v>3.818665376145934</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009947</v>
+        <v>3.843270952009945</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966256</v>
+        <v>3.845043810966254</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046992</v>
+        <v>3.79126997604699</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412099</v>
+        <v>3.735835647412095</v>
       </c>
       <c r="C1933" t="n">
         <v>2.903141953293337</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144512</v>
+        <v>3.762643902144508</v>
       </c>
       <c r="C1934" t="n">
         <v>2.925542446615903</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.72914282290069</v>
+        <v>3.729142822900687</v>
       </c>
       <c r="C1935" t="n">
         <v>2.925614847989315</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473598</v>
+        <v>3.743216620473595</v>
       </c>
       <c r="C1936" t="n">
         <v>2.936621770464017</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978366</v>
+        <v>3.714175563978363</v>
       </c>
       <c r="C1937" t="n">
         <v>2.927058479095908</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887699</v>
+        <v>3.710903155887696</v>
       </c>
       <c r="C1938" t="n">
         <v>2.751768044136295</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675896</v>
+        <v>3.746038950675892</v>
       </c>
       <c r="C1939" t="n">
         <v>2.756335276128083</v>
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.814168122586401</v>
+        <v>3.814168122586398</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.912647637581391</v>
+        <v>2.756346750014881</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.890482150215915</v>
+        <v>-4.005271956921875</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.19978599172797</v>
+        <v>1.153881542932383</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.5210965854263686</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.905711434567759</v>
+        <v>2.44368879875906</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240420.xlsx
+++ b/tame_output/ON/bt/strategyON_20240420.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-12.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>17.3%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-3.8%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.9%</t>
+          <t>-78.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>117.1%</t>
+          <t>116.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>136.9%</t>
+          <t>137.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.7%</t>
+          <t>95.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-706.0%</t>
+          <t>-708.2%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>29.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-57.4%</t>
+          <t>-57.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.7%</t>
+          <t>-74.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>97.1%</t>
+          <t>96.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>788.5%</t>
+          <t>782.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-1.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-562.1%</t>
+          <t>-552.1%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-277.0%</t>
+          <t>-277.9%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-41.5%</t>
+          <t>-40.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-260.8%</t>
+          <t>-256.9%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-32.9%</t>
+          <t>-33.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-26.3%</t>
+          <t>-27.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>31.3%</t>
+          <t>32.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-161.4%</t>
+          <t>-160.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-276.1%</t>
+          <t>-277.2%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>36.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.2%</t>
+          <t>-15.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-201.7%</t>
+          <t>-202.3%</t>
         </is>
       </c>
     </row>
@@ -44486,16 +44486,16 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097819</v>
+        <v>3.341378723097818</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.59703422617594</v>
+        <v>-7.761389467210065</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.0797085789085652</v>
+        <v>0.0139664824949155</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.799118819568881</v>
@@ -44509,16 +44509,16 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094115</v>
+        <v>3.374439043094116</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.942909048160748</v>
+        <v>-7.965101091585913</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.06254178473966299</v>
+        <v>-0.07141860210972872</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.799118819568881</v>
@@ -44532,16 +44532,16 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199284</v>
+        <v>3.405960511199285</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.255733847405727</v>
+        <v>-8.277925890830891</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1892667843826534</v>
+        <v>-0.1981436017527192</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.799118819568881</v>
@@ -44555,16 +44555,16 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969592</v>
+        <v>3.424633354969593</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.552395189215925</v>
+        <v>-8.57458723264109</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3041523451775245</v>
+        <v>-0.3130291625475903</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.867861955302759</v>
@@ -44578,16 +44578,16 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923086</v>
+        <v>3.419979433923087</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.985744297326161</v>
+        <v>-9.007936340751325</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.4815182929560216</v>
+        <v>-0.4903951103260873</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.867861955302759</v>
@@ -44601,16 +44601,16 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297749</v>
+        <v>3.45810009129775</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.368745686068792</v>
+        <v>-9.390937729493956</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.6348209497746584</v>
+        <v>-0.6436977671447242</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.867861955302759</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317616</v>
+        <v>3.447750501317617</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.743731012240069</v>
+        <v>-9.765923055665233</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.7822435642717389</v>
+        <v>-0.7911203816418046</v>
       </c>
       <c r="F1873" t="n">
         <v>-2.242847281474037</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.50351550673717</v>
+        <v>3.503515506737171</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.10326133474407</v>
+        <v>-10.12545337816923</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.9207053899752893</v>
+        <v>-0.929582207345355</v>
       </c>
       <c r="F1874" t="n">
         <v>-2.242847281474037</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341312</v>
+        <v>3.503170282341313</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.42966136340908</v>
+        <v>-10.45185340683425</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.043349381484117</v>
+        <v>-1.052226198854183</v>
       </c>
       <c r="F1875" t="n">
         <v>-2.56924731013905</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776676</v>
+        <v>3.500446096776677</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.64881033148328</v>
+        <v>-10.67100237490845</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.127967218092027</v>
+        <v>-1.136844035462093</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.788396278213247</v>
@@ -44716,16 +44716,16 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407493</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.64511940652687</v>
+        <v>-10.66731144995203</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.126490848109463</v>
+        <v>-1.135367665479528</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.788396278213247</v>
@@ -44739,16 +44739,16 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611696</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.84937758185673</v>
+        <v>-10.8715696252819</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.202680921122766</v>
+        <v>-1.211557738492832</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.916035222827236</v>
@@ -44768,10 +44768,10 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.06741535348791</v>
+        <v>-11.08960739691308</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.285413475290801</v>
+        <v>-1.294290292660867</v>
       </c>
       <c r="F1879" t="n">
         <v>-3.090805990923135</v>
@@ -44785,16 +44785,16 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910628</v>
+        <v>3.499968163910629</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.99394552182046</v>
+        <v>-11.01613756524563</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.2406538411304</v>
+        <v>-1.249530658500466</v>
       </c>
       <c r="F1880" t="n">
         <v>-3.017336159255687</v>
@@ -44808,16 +44808,16 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078595</v>
+        <v>3.490055666078596</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.16906993920701</v>
+        <v>-11.19126198263217</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.296148387337501</v>
+        <v>-1.305025204707567</v>
       </c>
       <c r="F1881" t="n">
         <v>-3.19246057664223</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880267</v>
+        <v>3.485875018880268</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.4035220332215</v>
+        <v>-11.42571407664666</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.397148389844892</v>
+        <v>-1.406025207214958</v>
       </c>
       <c r="F1882" t="n">
         <v>-3.19246057664223</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234391</v>
+        <v>3.480688917234392</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.69132587775873</v>
+        <v>-11.7135179211839</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.518942118433765</v>
+        <v>-1.52781893580383</v>
       </c>
       <c r="F1883" t="n">
         <v>-3.480264421179469</v>
@@ -44877,16 +44877,16 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860581</v>
+        <v>3.493712438860582</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.92115032492256</v>
+        <v>-11.94334236834772</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.609756107460738</v>
+        <v>-1.618632924830804</v>
       </c>
       <c r="F1884" t="n">
         <v>-3.642911958249629</v>
@@ -44900,16 +44900,16 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767395</v>
+        <v>3.492098065767396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.15317924465882</v>
+        <v>-12.17537128808399</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.699873946726128</v>
+        <v>-1.708750764096194</v>
       </c>
       <c r="F1885" t="n">
         <v>-3.704924655438052</v>
@@ -44923,16 +44923,16 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.57367044979254</v>
+        <v>3.573670449792541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.10116373069001</v>
+        <v>-12.12335577411517</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.675077405452202</v>
+        <v>-1.683954222822268</v>
       </c>
       <c r="F1886" t="n">
         <v>-3.704924655438052</v>
@@ -44946,16 +44946,16 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628917</v>
+        <v>3.600034689628918</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.24283557241413</v>
+        <v>-12.26502761583929</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.733221369040592</v>
+        <v>-1.742098186410658</v>
       </c>
       <c r="F1887" t="n">
         <v>-3.704924655438052</v>
@@ -44969,16 +44969,16 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410715</v>
+        <v>3.691568158410716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.3417423128734</v>
+        <v>-12.36393435629857</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.75773065505943</v>
+        <v>-1.766607472429496</v>
       </c>
       <c r="F1888" t="n">
         <v>-3.803831395897328</v>
@@ -44992,16 +44992,16 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240575</v>
+        <v>3.676837974240576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.1425902056363</v>
+        <v>-12.16478224906147</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.691120945811273</v>
+        <v>-1.699997763181339</v>
       </c>
       <c r="F1889" t="n">
         <v>-3.638508869947514</v>
@@ -45015,16 +45015,16 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085278</v>
+        <v>3.685157806085279</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.91674505291689</v>
+        <v>-11.93893709634206</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.5912038116873</v>
+        <v>-1.600080629057366</v>
       </c>
       <c r="F1890" t="n">
         <v>-3.596582194360351</v>
@@ -45038,16 +45038,16 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282098</v>
+        <v>3.684840248282099</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.6304702405942</v>
+        <v>-11.65266228401936</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.475554742202164</v>
+        <v>-1.48443155957223</v>
       </c>
       <c r="F1891" t="n">
         <v>-3.596582194360351</v>
@@ -45067,10 +45067,10 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.68336552863849</v>
+        <v>-11.70555757206365</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.494079083257771</v>
+        <v>-1.502955900627836</v>
       </c>
       <c r="F1892" t="n">
         <v>-3.591626848271904</v>
@@ -45084,16 +45084,16 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081564</v>
+        <v>3.768948099081565</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.39945679770974</v>
+        <v>-11.4216488411349</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.374781886647635</v>
+        <v>-1.383658704017701</v>
       </c>
       <c r="F1893" t="n">
         <v>-3.591626848271904</v>
@@ -45107,16 +45107,16 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425323</v>
+        <v>3.728574354425324</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.28403587357164</v>
+        <v>-11.30622791699681</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.338350779386261</v>
+        <v>-1.347227596756327</v>
       </c>
       <c r="F1894" t="n">
         <v>-3.476205924133809</v>
@@ -45130,16 +45130,16 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702407</v>
+        <v>3.747699084702408</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.02019900636757</v>
+        <v>-11.04239104979274</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.242699513817541</v>
+        <v>-1.251576331187607</v>
       </c>
       <c r="F1895" t="n">
         <v>-3.476205924133809</v>
@@ -45153,16 +45153,16 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906223</v>
+        <v>3.766313503906224</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.75295720549917</v>
+        <v>-10.77514924892434</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.137637353969555</v>
+        <v>-1.146514171339621</v>
       </c>
       <c r="F1896" t="n">
         <v>-3.476205924133809</v>
@@ -45176,16 +45176,16 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781943</v>
+        <v>3.784680945781945</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.62965127702095</v>
+        <v>-10.65184332044612</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.088615297551728</v>
+        <v>-1.097492114921794</v>
       </c>
       <c r="F1897" t="n">
         <v>-3.386788253006246</v>
@@ -45199,16 +45199,16 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567239</v>
+        <v>3.800825778567241</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.605697736045</v>
+        <v>-10.62788977947016</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.078365375015852</v>
+        <v>-1.087242192385918</v>
       </c>
       <c r="F1898" t="n">
         <v>-3.362834712030288</v>
@@ -45222,16 +45222,16 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487768</v>
+        <v>3.789307536487771</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.3416377977222</v>
+        <v>-10.36382984114736</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.9860017158484853</v>
+        <v>-0.994878533218551</v>
       </c>
       <c r="F1899" t="n">
         <v>-3.098774773707492</v>
@@ -45245,16 +45245,16 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309722</v>
+        <v>3.833249172309724</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.634558174217362</v>
+        <v>-9.656750217642527</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.7059569001068513</v>
+        <v>-0.714833717476917</v>
       </c>
       <c r="F1900" t="n">
         <v>-3.098774773707492</v>
@@ -45268,16 +45268,16 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858724</v>
+        <v>3.839370871858727</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.594373875851172</v>
+        <v>-9.616565919276336</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.6895395568725338</v>
+        <v>-0.6984163742425995</v>
       </c>
       <c r="F1901" t="n">
         <v>-3.058590475341301</v>
@@ -45291,16 +45291,16 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.85615817609647</v>
+        <v>3.856158176096473</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.514304080313368</v>
+        <v>-9.536496123738532</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.6581448174366553</v>
+        <v>-0.6670216348067211</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.978520679803497</v>
@@ -45314,16 +45314,16 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761806</v>
+        <v>3.787326853761809</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.28082285808377</v>
+        <v>-9.303014901508934</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.5568278997069638</v>
+        <v>-0.5657047170770295</v>
       </c>
       <c r="F1903" t="n">
         <v>-2.745039457573899</v>
@@ -45337,16 +45337,16 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255783</v>
+        <v>3.801633547255786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.101114327939896</v>
+        <v>-9.123306371365061</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.4878366979623734</v>
+        <v>-0.4967135153324391</v>
       </c>
       <c r="F1904" t="n">
         <v>-2.687867953411203</v>
@@ -45360,16 +45360,16 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860423</v>
+        <v>3.763178672860427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.968838854309009</v>
+        <v>-8.991030897734174</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.4395590217629914</v>
+        <v>-0.4484358391330572</v>
       </c>
       <c r="F1905" t="n">
         <v>-2.555592479780316</v>
@@ -45383,16 +45383,16 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575948</v>
+        <v>3.784715218575951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.778239179635856</v>
+        <v>-8.80043122306102</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.3605040912060935</v>
+        <v>-0.3693809085761592</v>
       </c>
       <c r="F1906" t="n">
         <v>-2.364992805107164</v>
@@ -45406,16 +45406,16 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430983</v>
+        <v>3.753878996430987</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.529239380952275</v>
+        <v>-8.551431424377439</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.2479978305090023</v>
+        <v>-0.256874647879068</v>
       </c>
       <c r="F1907" t="n">
         <v>-2.364992805107164</v>
@@ -45429,16 +45429,16 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.69292828007764</v>
+        <v>3.692928280077644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.634829370725379</v>
+        <v>-8.657021414150543</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4182097560174629</v>
+        <v>-0.4270865733875286</v>
       </c>
       <c r="F1908" t="n">
         <v>-2.470582794880268</v>
@@ -45452,16 +45452,16 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457898</v>
+        <v>3.770419008457901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.653564272843976</v>
+        <v>-8.67575631626914</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.3771593749878153</v>
+        <v>-0.386036192357881</v>
       </c>
       <c r="F1909" t="n">
         <v>-2.470582794880268</v>
@@ -45475,16 +45475,16 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180807</v>
+        <v>3.76033011118081</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.505624231436377</v>
+        <v>-8.527816274861541</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.4378622811129431</v>
+        <v>-0.4467390984830089</v>
       </c>
       <c r="F1910" t="n">
         <v>-2.45026187897171</v>
@@ -45498,16 +45498,16 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879199</v>
+        <v>3.723562653879203</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.378731825001307</v>
+        <v>-8.400923868426471</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.395819304792393</v>
+        <v>-0.4046961221624588</v>
       </c>
       <c r="F1911" t="n">
         <v>-2.323369472536641</v>
@@ -45521,16 +45521,16 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568103</v>
+        <v>3.729966140568107</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.335183418230615</v>
+        <v>-8.35737546165578</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.3853605541792096</v>
+        <v>-0.3942373715492753</v>
       </c>
       <c r="F1912" t="n">
         <v>-2.323369472536641</v>
@@ -45544,16 +45544,16 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963414</v>
+        <v>3.782918957963417</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.093035024776757</v>
+        <v>-8.115227068201921</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.2740388424165232</v>
+        <v>-0.2829156597865889</v>
       </c>
       <c r="F1913" t="n">
         <v>-2.323369472536641</v>
@@ -45567,16 +45567,16 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.82854791119281</v>
+        <v>3.828547911192814</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.02980565300841</v>
+        <v>-8.051997696433574</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.2542149732499892</v>
+        <v>-0.2630917906200549</v>
       </c>
       <c r="F1914" t="n">
         <v>-2.323369472536641</v>
@@ -45590,16 +45590,16 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.82804935326204</v>
+        <v>3.828049353262044</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.843317960631404</v>
+        <v>-7.865510004056568</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.1821218022886102</v>
+        <v>-0.1909986196586759</v>
       </c>
       <c r="F1915" t="n">
         <v>-2.136881780159634</v>
@@ -45613,16 +45613,16 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389902</v>
+        <v>3.812450103389906</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.82216876172796</v>
+        <v>-7.844360805153125</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.1659611444899074</v>
+        <v>-0.1748379618599731</v>
       </c>
       <c r="F1916" t="n">
         <v>-2.115732581256191</v>
@@ -45636,16 +45636,16 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788088</v>
+        <v>3.748324832788091</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.578403319744516</v>
+        <v>-7.60059536316968</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.07267425934947935</v>
+        <v>-0.08155107671954509</v>
       </c>
       <c r="F1917" t="n">
         <v>-2.115732581256191</v>
@@ -45659,16 +45659,16 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.82430765752752</v>
+        <v>3.824307657527523</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.314375252551256</v>
+        <v>-7.336567295976421</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.03506128144784082</v>
+        <v>0.02618446407777508</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.913867182440237</v>
@@ -45682,16 +45682,16 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749178</v>
+        <v>3.826351398749182</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.064524858602182</v>
+        <v>-7.086716902027346</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.1277435140111725</v>
+        <v>0.1188666966411067</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.913867182440237</v>
@@ -45705,16 +45705,16 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481492</v>
+        <v>3.835954411481495</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.760957369598203</v>
+        <v>-6.783149413023367</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.2527696331334131</v>
+        <v>0.2438928157633473</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.913867182440237</v>
@@ -45728,16 +45728,16 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862981</v>
+        <v>3.780930335862984</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.687477460746189</v>
+        <v>-6.709669504171353</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.295489102728772</v>
+        <v>0.2866122853587063</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.840387273588223</v>
@@ -45751,16 +45751,16 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102775</v>
+        <v>3.773761647102779</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.462444461077366</v>
+        <v>-6.48463650450253</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.3845227802125981</v>
+        <v>0.3756459628425324</v>
       </c>
       <c r="F1922" t="n">
         <v>-1.6153542739194</v>
@@ -45774,16 +45774,16 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353067</v>
+        <v>3.764614304353071</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.247810083440959</v>
+        <v>-6.270002126866124</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.4750713323214781</v>
+        <v>0.4661945149514124</v>
       </c>
       <c r="F1923" t="n">
         <v>-1.400719896282993</v>
@@ -45797,16 +45797,16 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544776</v>
+        <v>3.798811195544779</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.981209726466608</v>
+        <v>-6.003401769891772</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.5629057338950147</v>
+        <v>0.554028916524949</v>
       </c>
       <c r="F1924" t="n">
         <v>-1.400719896282993</v>
@@ -45820,16 +45820,16 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712287</v>
+        <v>3.797691308712291</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.740779229661747</v>
+        <v>-5.762971273086912</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.6608210092418361</v>
+        <v>0.6519441918717703</v>
       </c>
       <c r="F1925" t="n">
         <v>-1.160289399478133</v>
@@ -45843,16 +45843,16 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837679</v>
+        <v>3.821589933837682</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.497988422012302</v>
+        <v>-5.520180465437466</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7618666461364345</v>
+        <v>0.7529898287663688</v>
       </c>
       <c r="F1926" t="n">
         <v>-1.160289399478133</v>
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.82232342234996</v>
+        <v>3.822323422349964</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.258383330405213</v>
+        <v>-5.435257126416282</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8583872666966101</v>
+        <v>0.7876377482921826</v>
       </c>
       <c r="F1927" t="n">
-        <v>-1.093241451809638</v>
+        <v>-1.10453185671121</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.30615215208666</v>
+        <v>2.299377909145717</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972333</v>
+        <v>3.848613050972337</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.015727741982049</v>
+        <v>-5.192601537993118</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9524475732858693</v>
+        <v>0.8816980548814417</v>
       </c>
       <c r="F1928" t="n">
-        <v>-1.093241451809638</v>
+        <v>-1.10453185671121</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.303150223306653</v>
+        <v>2.29637598036571</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145934</v>
+        <v>3.818665376145938</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.795706943945039</v>
+        <v>-4.972580739956108</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.042034929511288</v>
+        <v>0.9712854111068598</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.9520216067416583</v>
+        <v>-0.9633120116432299</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.389461167358056</v>
+        <v>2.382686924417113</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009945</v>
+        <v>3.843270952009949</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.59645831404023</v>
+        <v>-4.773332110051299</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.137628564275035</v>
+        <v>1.066879045870607</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.9520216067416583</v>
+        <v>-0.9633120116432299</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.405355350159879</v>
+        <v>2.398581107218936</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966254</v>
+        <v>3.845043810966257</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.43694321052086</v>
+        <v>-4.613817006531929</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.202580450123084</v>
+        <v>1.131830931718657</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.7925065032222883</v>
+        <v>-0.80379690812386</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.502210256711803</v>
+        <v>2.49543601377086</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.79126997604699</v>
+        <v>3.791269976046993</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.292271065421122</v>
+        <v>-4.469144861432191</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.270537410724419</v>
+        <v>1.199787892319991</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.647834358122551</v>
+        <v>-0.6591247630241226</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.599101646333085</v>
+        <v>2.592327403392142</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412095</v>
+        <v>3.735835647412099</v>
       </c>
       <c r="C1933" t="n">
         <v>2.903141953293337</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.274501606490166</v>
+        <v>-4.451375402501236</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.192984886383523</v>
+        <v>1.122235367979096</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.6300648991915954</v>
+        <v>-0.641355304093167</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.52510301377838</v>
+        <v>2.518328770837437</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144508</v>
+        <v>3.762643902144512</v>
       </c>
       <c r="C1934" t="n">
         <v>2.925542446615903</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.187702108711157</v>
+        <v>-4.364575904722226</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.250105178817693</v>
+        <v>1.179355660413265</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.6300648991915954</v>
+        <v>-0.641355304093167</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.547503507100946</v>
+        <v>2.540729264160003</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900687</v>
+        <v>3.72914282290069</v>
       </c>
       <c r="C1935" t="n">
         <v>2.925614847989315</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.088009493982145</v>
+        <v>-4.264883289993215</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.29005462608271</v>
+        <v>1.219305107678282</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.5303722844625836</v>
+        <v>-0.5416626893641552</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.607391477311765</v>
+        <v>2.600617234370822</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473595</v>
+        <v>3.743216620473598</v>
       </c>
       <c r="C1936" t="n">
         <v>2.936621770464017</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.156379680306156</v>
+        <v>-4.333253476317225</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.273713474027808</v>
+        <v>1.20296395562338</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.5210965854263686</v>
+        <v>-0.5323869903279402</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.623963819208196</v>
+        <v>2.617189576267253</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978363</v>
+        <v>3.714175563978366</v>
       </c>
       <c r="C1937" t="n">
         <v>2.927058479095908</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.034963250679679</v>
+        <v>-4.211837046690748</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.31271675451029</v>
+        <v>1.241967236105862</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.5210965854263686</v>
+        <v>-0.5323869903279402</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.614400527840087</v>
+        <v>2.607626284899144</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887696</v>
+        <v>3.710903155887699</v>
       </c>
       <c r="C1938" t="n">
         <v>2.751768044136295</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.065956410008384</v>
+        <v>-4.242830206019454</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.125029055819194</v>
+        <v>1.054279537414767</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.5210965854263686</v>
+        <v>-0.5323869903279402</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.439110092880474</v>
+        <v>2.432335849939531</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675892</v>
+        <v>3.746038950675896</v>
       </c>
       <c r="C1939" t="n">
         <v>2.756335276128083</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.890482150215915</v>
+        <v>-4.067355946226984</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.19978599172797</v>
+        <v>1.129036473323542</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.5210965854263686</v>
+        <v>-0.5323869903279402</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.443677324872262</v>
+        <v>2.436903081931319</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.814168122586398</v>
+        <v>3.45416098643141</v>
       </c>
       <c r="C1940" t="n">
         <v>2.756346750014881</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.005271956921875</v>
+        <v>-3.905704443240547</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.153881542932383</v>
+        <v>1.193708548404915</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.5210965854263686</v>
+        <v>-0.5323869903279402</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.44368879875906</v>
+        <v>2.436914555818117</v>
       </c>
     </row>
   </sheetData>
